--- a/data/trans_camb/IP24_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,61; -4,63</t>
+          <t>-23,06; -5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,15; -0,31</t>
+          <t>-19,43; -1,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-39,26; -16,62</t>
+          <t>-38,33; -15,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 3,31</t>
+          <t>-15,36; 2,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,59; -2,65</t>
+          <t>-22,17; -1,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,94; -6,95</t>
+          <t>-28,86; -5,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,36; -3,66</t>
+          <t>-17,29; -3,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,59; -3,57</t>
+          <t>-18,07; -4,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,27; -13,85</t>
+          <t>-31,1; -13,55</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,94; -6,9</t>
+          <t>-30,08; -7,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,37; -0,44</t>
+          <t>-25,16; -1,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,74; -23,61</t>
+          <t>-52,08; -22,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 4,96</t>
+          <t>-20,32; 4,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,1; -3,83</t>
+          <t>-29,55; -2,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,14; -10,7</t>
+          <t>-39,95; -8,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-22,33; -5,53</t>
+          <t>-23,5; -5,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,34; -5,21</t>
+          <t>-23,7; -6,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,88; -20,14</t>
+          <t>-41,75; -19,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,88; -3,49</t>
+          <t>-13,78; -2,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 0,44</t>
+          <t>-10,49; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 7,69</t>
+          <t>-5,8; 8,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,04; -10,84</t>
+          <t>-20,65; -10,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,71; -2,95</t>
+          <t>-13,82; -3,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 0,9</t>
+          <t>-11,4; 0,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -8,57</t>
+          <t>-15,95; -8,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,6; -2,74</t>
+          <t>-10,79; -2,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,33</t>
+          <t>-7,07; 2,06</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,61; -17,5</t>
+          <t>-58,78; -12,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 2,59</t>
+          <t>-45,33; 8,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 44,14</t>
+          <t>-26,37; 46,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,61; -57,02</t>
+          <t>-82,45; -57,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,94; -16,24</t>
+          <t>-56,42; -16,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,25; 5,52</t>
+          <t>-47,41; 3,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,27; -44,98</t>
+          <t>-68,93; -45,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,52; -14,53</t>
+          <t>-46,61; -15,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 12,48</t>
+          <t>-30,78; 11,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -3,13</t>
+          <t>-14,1; -3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 0,72</t>
+          <t>-10,44; 1,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 6,54</t>
+          <t>-6,33; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -4,42</t>
+          <t>-13,04; -5,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,56; -1,47</t>
+          <t>-10,71; -1,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 10,03</t>
+          <t>-1,72; 9,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; -5,08</t>
+          <t>-11,84; -5,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -1,28</t>
+          <t>-9,03; -1,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 6,4</t>
+          <t>-2,38; 6,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,37; -28,07</t>
+          <t>-85,38; -29,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,31; 11,88</t>
+          <t>-64,65; 16,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 69,26</t>
+          <t>-41,45; 73,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-96,49; -58,38</t>
+          <t>-96,58; -56,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,04; -14,46</t>
+          <t>-81,4; -14,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 140,73</t>
+          <t>-14,59; 139,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,51; -57,34</t>
+          <t>-87,24; -54,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,51; -14,28</t>
+          <t>-67,07; -15,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,35; 71,96</t>
+          <t>-18,28; 72,16</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 5,74</t>
+          <t>-5,55; 6,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 6,21</t>
+          <t>-5,47; 6,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 39,21</t>
+          <t>3,24; 35,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 1,71</t>
+          <t>-5,96; 1,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,13</t>
+          <t>-5,55; 3,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 18,1</t>
+          <t>2,37; 19,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,78</t>
+          <t>-4,65; 2,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 3,09</t>
+          <t>-4,55; 3,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 24,53</t>
+          <t>4,4; 24,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 51,84</t>
+          <t>-32,6; 63,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-36,42; 55,5</t>
+          <t>-33,74; 58,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,3; 368,05</t>
+          <t>20,59; 329,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 31,68</t>
+          <t>-62,98; 38,59</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,45; 59,24</t>
+          <t>-58,95; 58,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,0; 321,44</t>
+          <t>24,6; 297,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,92; 30,72</t>
+          <t>-37,61; 30,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,37; 33,58</t>
+          <t>-35,59; 34,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>33,26; 241,47</t>
+          <t>36,88; 245,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,28; -1,05</t>
+          <t>-9,12; -1,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,31</t>
+          <t>-6,98; 0,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 9,66</t>
+          <t>-7,25; 9,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,07; -4,36</t>
+          <t>-10,8; -4,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -3,37</t>
+          <t>-9,94; -3,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -0,8</t>
+          <t>-9,1; -1,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; -3,79</t>
+          <t>-8,7; -3,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,45; -2,43</t>
+          <t>-7,51; -2,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 1,32</t>
+          <t>-7,09; 1,64</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,25; -4,38</t>
+          <t>-33,24; -6,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 1,27</t>
+          <t>-25,87; 0,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,93; 38,39</t>
+          <t>-27,24; 40,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -19,22</t>
+          <t>-43,37; -19,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -15,81</t>
+          <t>-39,48; -14,66</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -2,86</t>
+          <t>-36,66; -3,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,85; -16,41</t>
+          <t>-33,7; -16,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -10,78</t>
+          <t>-29,17; -10,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 5,63</t>
+          <t>-28,18; 7,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,06; -5,25</t>
+          <t>-23,73; -4,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,43; -1,23</t>
+          <t>-18,64; 0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-38,33; -15,64</t>
+          <t>-40,64; -15,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 2,95</t>
+          <t>-14,68; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,17; -1,97</t>
+          <t>-22,07; -2,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-28,86; -5,36</t>
+          <t>-29,67; -5,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -3,67</t>
+          <t>-16,36; -3,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -4,72</t>
+          <t>-16,86; -4,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -13,55</t>
+          <t>-31,03; -13,65</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,08; -7,77</t>
+          <t>-30,81; -6,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,16; -1,25</t>
+          <t>-24,19; 0,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,08; -22,75</t>
+          <t>-53,86; -22,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 4,45</t>
+          <t>-19,46; 6,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,55; -2,94</t>
+          <t>-29,85; -3,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,95; -8,56</t>
+          <t>-40,25; -8,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-23,5; -5,25</t>
+          <t>-21,67; -5,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,7; -6,58</t>
+          <t>-22,62; -6,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,75; -19,24</t>
+          <t>-41,66; -19,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -2,42</t>
+          <t>-14,11; -2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 1,19</t>
+          <t>-11,14; 0,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 8,48</t>
+          <t>-6,05; 8,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,65; -10,49</t>
+          <t>-20,5; -10,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,82; -3,12</t>
+          <t>-13,28; -2,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 0,66</t>
+          <t>-11,75; 0,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,95; -8,83</t>
+          <t>-15,77; -8,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,79; -2,88</t>
+          <t>-10,51; -2,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 2,06</t>
+          <t>-7,67; 2,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-58,78; -12,62</t>
+          <t>-59,74; -13,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,33; 8,08</t>
+          <t>-46,83; 3,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 46,84</t>
+          <t>-26,3; 44,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,45; -57,07</t>
+          <t>-82,21; -54,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,42; -16,43</t>
+          <t>-55,45; -14,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 3,95</t>
+          <t>-48,76; 3,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,93; -45,26</t>
+          <t>-68,7; -44,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,61; -15,09</t>
+          <t>-45,81; -15,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 11,02</t>
+          <t>-32,97; 10,44</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,1; -3,28</t>
+          <t>-13,91; -3,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 1,34</t>
+          <t>-10,06; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,52</t>
+          <t>-7,12; 5,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -5,03</t>
+          <t>-13,0; -4,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -1,35</t>
+          <t>-10,71; -1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 9,66</t>
+          <t>-2,18; 9,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -5,09</t>
+          <t>-11,7; -5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,03; -1,33</t>
+          <t>-8,67; -1,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 6,28</t>
+          <t>-2,58; 6,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,38; -29,09</t>
+          <t>-84,8; -28,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,65; 16,75</t>
+          <t>-65,77; 9,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 73,33</t>
+          <t>-43,91; 59,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-96,58; -56,5</t>
+          <t>-96,7; -54,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,4; -14,53</t>
+          <t>-81,99; -20,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 139,23</t>
+          <t>-19,54; 141,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-87,24; -54,74</t>
+          <t>-86,95; -54,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-67,07; -15,29</t>
+          <t>-64,43; -13,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 72,16</t>
+          <t>-19,54; 75,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 6,75</t>
+          <t>-5,33; 7,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 6,46</t>
+          <t>-5,73; 5,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 35,57</t>
+          <t>3,19; 36,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 1,98</t>
+          <t>-6,63; 1,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,23</t>
+          <t>-5,83; 3,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 19,57</t>
+          <t>2,55; 17,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,57</t>
+          <t>-4,61; 2,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,03</t>
+          <t>-4,02; 3,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 24,58</t>
+          <t>4,37; 23,83</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 63,96</t>
+          <t>-31,21; 65,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-33,74; 58,19</t>
+          <t>-35,36; 51,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,59; 329,18</t>
+          <t>20,02; 333,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-62,98; 38,59</t>
+          <t>-66,47; 28,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 58,88</t>
+          <t>-59,6; 58,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,6; 297,57</t>
+          <t>22,74; 307,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 30,83</t>
+          <t>-37,43; 30,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 34,5</t>
+          <t>-32,52; 39,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>36,88; 245,1</t>
+          <t>34,61; 246,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -1,51</t>
+          <t>-9,05; -1,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 0,18</t>
+          <t>-7,13; 0,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 9,15</t>
+          <t>-7,26; 9,1</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -4,13</t>
+          <t>-10,97; -3,99</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -3,15</t>
+          <t>-9,93; -3,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,1; -1,0</t>
+          <t>-9,11; -1,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,7; -3,77</t>
+          <t>-8,75; -3,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -2,51</t>
+          <t>-7,37; -2,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 1,64</t>
+          <t>-7,29; 1,3</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -6,87</t>
+          <t>-32,4; -7,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 0,61</t>
+          <t>-26,49; 1,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 40,97</t>
+          <t>-27,22; 36,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,37; -19,05</t>
+          <t>-43,18; -18,03</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,48; -14,66</t>
+          <t>-39,49; -15,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; -3,81</t>
+          <t>-36,26; -3,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,7; -16,19</t>
+          <t>-34,43; -16,05</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,17; -10,86</t>
+          <t>-29,05; -11,03</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 7,27</t>
+          <t>-28,68; 6,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP24_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP24_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-5,77</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-12,24</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-18,54</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-14,33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-9,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-27,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,77</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-12,24</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,5</t>
+          <t>-30,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-22,88</t>
+          <t>-24,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,73; -4,46</t>
+          <t>-15,34; 3,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 0,43</t>
+          <t>-21,59; -2,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-40,64; -15,45</t>
+          <t>-30,23; -6,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 4,18</t>
+          <t>-23,61; -4,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-22,07; -2,35</t>
+          <t>-19,15; -0,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,67; -5,55</t>
+          <t>-42,42; -19,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,36; -3,44</t>
+          <t>-16,36; -3,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -4,24</t>
+          <t>-17,59; -3,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-31,03; -13,65</t>
+          <t>-33,0; -15,54</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-8,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-17,26%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-26,16%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-19,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-13,45%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-37,82%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-8,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-17,26%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-26,1%</t>
+          <t>-42,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-31,87%</t>
+          <t>-34,37%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,81; -6,88</t>
+          <t>-20,16; 4,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 0,51</t>
+          <t>-29,1; -3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,86; -22,99</t>
+          <t>-41,1; -10,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 6,58</t>
+          <t>-30,94; -6,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,85; -3,87</t>
+          <t>-24,37; -0,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-40,25; -8,82</t>
+          <t>-55,48; -27,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,67; -5,05</t>
+          <t>-22,33; -5,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,62; -6,08</t>
+          <t>-23,34; -5,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,66; -19,2</t>
+          <t>-44,25; -22,67</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-15,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-8,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-6,37</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-8,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-5,16</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-15,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-8,01</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,55</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,66</t>
+          <t>-4,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -2,77</t>
+          <t>-20,04; -10,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 0,6</t>
+          <t>-13,71; -2,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 8,21</t>
+          <t>-12,59; -0,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,5; -10,89</t>
+          <t>-13,88; -3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,28; -2,67</t>
+          <t>-10,72; 0,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 0,63</t>
+          <t>-9,18; 3,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,77; -8,63</t>
+          <t>-15,71; -8,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; -2,92</t>
+          <t>-10,6; -2,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 2,0</t>
+          <t>-8,86; 0,19</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-71,73%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-37,41%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-29,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-41,55%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-25,11%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-71,73%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-37,41%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-25,9%</t>
+          <t>-13,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-12,67%</t>
+          <t>-21,83%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,74; -13,56</t>
+          <t>-82,61; -57,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,83; 3,88</t>
+          <t>-55,94; -16,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 44,18</t>
+          <t>-51,43; -1,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,21; -54,67</t>
+          <t>-59,61; -17,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,45; -14,27</t>
+          <t>-46,66; 2,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 3,7</t>
+          <t>-40,21; 19,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,7; -44,37</t>
+          <t>-68,27; -44,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -15,24</t>
+          <t>-46,52; -14,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 10,44</t>
+          <t>-38,66; 1,06</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-8,43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,69</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-8,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,33</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-8,43</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,69</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>1,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,91; -3,14</t>
+          <t>-13,06; -4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 0,7</t>
+          <t>-10,56; -1,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 5,7</t>
+          <t>-3,07; 8,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; -4,45</t>
+          <t>-13,6; -3,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -1,7</t>
+          <t>-10,78; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,43</t>
+          <t>-6,27; 6,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -5,0</t>
+          <t>-11,56; -5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,67; -1,38</t>
+          <t>-8,62; -1,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,36</t>
+          <t>-2,64; 5,81</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-86,99%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-58,72%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26,6%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-66,07%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-35,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-1,83%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-86,99%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-58,72%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>-0,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,8; -28,57</t>
+          <t>-96,49; -58,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 9,73</t>
+          <t>-81,04; -14,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 59,82</t>
+          <t>-27,93; 123,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-96,7; -54,67</t>
+          <t>-84,37; -28,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-81,99; -20,58</t>
+          <t>-66,31; 11,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 141,88</t>
+          <t>-39,8; 72,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,95; -54,49</t>
+          <t>-87,51; -57,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,43; -13,85</t>
+          <t>-65,51; -14,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-19,54; 75,58</t>
+          <t>-20,32; 65,37</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,17</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13,44</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,91</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10,46</t>
+          <t>4,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 7,02</t>
+          <t>-6,24; 1,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 5,95</t>
+          <t>-5,13; 3,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 36,16</t>
+          <t>1,45; 15,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 1,62</t>
+          <t>-5,8; 5,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,12</t>
+          <t>-5,97; 6,21</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 17,79</t>
+          <t>-2,67; 9,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 2,94</t>
+          <t>-4,6; 2,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,55</t>
+          <t>-4,3; 3,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 23,83</t>
+          <t>0,87; 10,12</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-29,22%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-17,02%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-29,22%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-17,02%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>103,61%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,21; 65,07</t>
+          <t>-64,31; 31,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 51,73</t>
+          <t>-54,45; 59,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,02; 333,16</t>
+          <t>9,5; 276,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 28,89</t>
+          <t>-34,23; 51,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 58,58</t>
+          <t>-36,42; 55,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,74; 307,63</t>
+          <t>-16,89; 81,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 30,87</t>
+          <t>-36,92; 30,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 39,09</t>
+          <t>-34,37; 33,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34,61; 246,67</t>
+          <t>4,02; 107,47</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-7,47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,61</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-6,87</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-4,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-3,34</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,89</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-7,47</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-6,61</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-5,53</t>
+          <t>-7,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-7,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,05; -1,79</t>
+          <t>-11,07; -4,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 0,41</t>
+          <t>-9,96; -3,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 9,1</t>
+          <t>-10,3; -2,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,97; -3,99</t>
+          <t>-8,28; -1,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -3,12</t>
+          <t>-7,23; 0,31</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,07</t>
+          <t>-11,43; -3,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -3,63</t>
+          <t>-8,88; -3,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,57</t>
+          <t>-7,45; -2,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,3</t>
+          <t>-9,58; -4,18</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-31,9%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-28,24%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-29,33%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-19,64%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-13,19%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-7,45%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-31,9%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-28,24%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-23,61%</t>
+          <t>-29,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-15,87%</t>
+          <t>-29,42%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,4; -7,15</t>
+          <t>-43,41; -19,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 1,72</t>
+          <t>-39,55; -15,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 36,41</t>
+          <t>-41,16; -10,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,18; -18,03</t>
+          <t>-30,25; -4,38</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-39,49; -15,01</t>
+          <t>-26,46; 1,27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -3,39</t>
+          <t>-41,52; -15,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,05</t>
+          <t>-34,85; -16,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -11,03</t>
+          <t>-29,16; -10,78</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 6,01</t>
+          <t>-37,77; -17,73</t>
         </is>
       </c>
     </row>
